--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ПОДИ ЕООД/ПОДИ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ПОДИ ЕООД/ПОДИ ЕООД.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="ПОДИ ЕООД" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="157">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -82,6 +85,54 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>1172 Русе Шелф</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1179 Русе, Липник</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
     <t>Туба2</t>
   </si>
   <si>
@@ -94,12 +145,12 @@
     <t>Туба1</t>
   </si>
   <si>
+    <t>B12563</t>
+  </si>
+  <si>
     <t>В11969</t>
   </si>
   <si>
-    <t>B12563</t>
-  </si>
-  <si>
     <t>В08283</t>
   </si>
   <si>
@@ -112,6 +163,18 @@
     <t>С6524НС</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>B9415TC</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>В3771ТР</t>
+  </si>
+  <si>
     <t>78970153027720753</t>
   </si>
   <si>
@@ -124,12 +187,12 @@
     <t>78970153027720746</t>
   </si>
   <si>
+    <t>78970153027720191</t>
+  </si>
+  <si>
     <t>78970153027720027</t>
   </si>
   <si>
-    <t>78970153027720191</t>
-  </si>
-  <si>
     <t>78970153027720019</t>
   </si>
   <si>
@@ -142,67 +205,268 @@
     <t>78970153027720118</t>
   </si>
   <si>
+    <t>78970153027720217</t>
+  </si>
+  <si>
+    <t>78970153027720142</t>
+  </si>
+  <si>
+    <t>78970153027720043</t>
+  </si>
+  <si>
+    <t>78970153027720076</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>07:01</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>08:29</t>
-  </si>
-  <si>
-    <t>13:08</t>
-  </si>
-  <si>
-    <t>16:23</t>
-  </si>
-  <si>
-    <t>06:37</t>
-  </si>
-  <si>
-    <t>17:16</t>
-  </si>
-  <si>
-    <t>14:58</t>
-  </si>
-  <si>
-    <t>07:09</t>
-  </si>
-  <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>19:16</t>
-  </si>
-  <si>
-    <t>09:36</t>
-  </si>
-  <si>
-    <t>14:17</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>06:57</t>
+    <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>EKO RACING 100</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>07:00:00</t>
+  </si>
+  <si>
+    <t>17:39:00</t>
+  </si>
+  <si>
+    <t>05:05:00</t>
+  </si>
+  <si>
+    <t>06:16:00</t>
+  </si>
+  <si>
+    <t>08:29:00</t>
+  </si>
+  <si>
+    <t>13:08:00</t>
+  </si>
+  <si>
+    <t>06:36:00</t>
+  </si>
+  <si>
+    <t>16:23:00</t>
+  </si>
+  <si>
+    <t>17:15:00</t>
+  </si>
+  <si>
+    <t>14:58:00</t>
+  </si>
+  <si>
+    <t>07:08:00</t>
+  </si>
+  <si>
+    <t>05:11:00</t>
+  </si>
+  <si>
+    <t>06:05:00</t>
+  </si>
+  <si>
+    <t>15:10:00</t>
+  </si>
+  <si>
+    <t>19:17:00</t>
+  </si>
+  <si>
+    <t>09:36:00</t>
+  </si>
+  <si>
+    <t>14:17:00</t>
+  </si>
+  <si>
+    <t>06:35:00</t>
+  </si>
+  <si>
+    <t>06:56:00</t>
+  </si>
+  <si>
+    <t>07:04:00</t>
+  </si>
+  <si>
+    <t>11:24:00</t>
+  </si>
+  <si>
+    <t>07:49:00</t>
+  </si>
+  <si>
+    <t>06:54:00</t>
+  </si>
+  <si>
+    <t>17:28:00</t>
+  </si>
+  <si>
+    <t>08:43:00</t>
+  </si>
+  <si>
+    <t>13:23:00</t>
+  </si>
+  <si>
+    <t>13:01:00</t>
+  </si>
+  <si>
+    <t>16:50:00</t>
+  </si>
+  <si>
+    <t>06:30:00</t>
+  </si>
+  <si>
+    <t>06:26:00</t>
+  </si>
+  <si>
+    <t>05:08:00</t>
+  </si>
+  <si>
+    <t>07:09:00</t>
+  </si>
+  <si>
+    <t>12:09:00</t>
+  </si>
+  <si>
+    <t>18:12:00</t>
+  </si>
+  <si>
+    <t>13:29:00</t>
+  </si>
+  <si>
+    <t>15:50:00</t>
+  </si>
+  <si>
+    <t>14:10:00</t>
+  </si>
+  <si>
+    <t>16:43:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>3231285416 3231285416</t>
+  </si>
+  <si>
+    <t>3231297589 3231297589</t>
+  </si>
+  <si>
+    <t>3231382322 3231382322</t>
+  </si>
+  <si>
+    <t>3231401671 3231401671</t>
+  </si>
+  <si>
+    <t>3231384475 3231384475</t>
+  </si>
+  <si>
+    <t>3231407374 3231407374</t>
+  </si>
+  <si>
+    <t>3231448812 3231448812</t>
+  </si>
+  <si>
+    <t>3231458642 3231458642</t>
+  </si>
+  <si>
+    <t>3231541242 3231541242</t>
+  </si>
+  <si>
+    <t>3231604438 3231604438</t>
+  </si>
+  <si>
+    <t>3231562188 3231562188</t>
+  </si>
+  <si>
+    <t>3231696715 3231696715</t>
+  </si>
+  <si>
+    <t>3231727226 3231727226</t>
+  </si>
+  <si>
+    <t>3231735079 3231735079</t>
+  </si>
+  <si>
+    <t>3231768990 3231768990</t>
+  </si>
+  <si>
+    <t>3231772068 3231772068</t>
+  </si>
+  <si>
+    <t>3231874121 3231874121</t>
+  </si>
+  <si>
+    <t>3231894246 3231894246</t>
+  </si>
+  <si>
+    <t>3231922914 3231922914</t>
+  </si>
+  <si>
+    <t>3232051642 3232051642</t>
+  </si>
+  <si>
+    <t>3232056940 3232056940</t>
+  </si>
+  <si>
+    <t>3232099833 3232099833</t>
+  </si>
+  <si>
+    <t>3232099827 3232099827</t>
+  </si>
+  <si>
+    <t>3232109185 3232109185</t>
+  </si>
+  <si>
+    <t>3232153992 3232153992</t>
+  </si>
+  <si>
+    <t>3232192533 3232192533</t>
+  </si>
+  <si>
+    <t>3232197385 3232197385</t>
+  </si>
+  <si>
+    <t>3232360419 3232360419</t>
+  </si>
+  <si>
+    <t>3232375441 3232375441</t>
+  </si>
+  <si>
+    <t>3232379943 3232379943</t>
+  </si>
+  <si>
+    <t>3232399566 3232399566</t>
+  </si>
+  <si>
+    <t>3232400911 3232400911</t>
+  </si>
+  <si>
+    <t>3232476209 3232476209</t>
+  </si>
+  <si>
+    <t>3232485480 3232485480</t>
+  </si>
+  <si>
+    <t>3232473352 3232473352</t>
+  </si>
+  <si>
+    <t>3232478006 3232478006</t>
+  </si>
+  <si>
+    <t>3232527434 3232527434</t>
+  </si>
+  <si>
+    <t>3232548250 3232548250</t>
+  </si>
+  <si>
+    <t>3232579256 3232579256</t>
+  </si>
+  <si>
+    <t>3232642807 3232642807</t>
   </si>
   <si>
     <t>Общи литри по продукт / ПОДИ ЕООД</t>
@@ -626,24 +890,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -683,918 +949,1945 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1172</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F2">
         <v>50.71</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2">
         <v>1.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>84.18000000000001</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>91.28</v>
       </c>
-      <c r="K2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+      <c r="L2" t="s">
+        <v>72</v>
       </c>
       <c r="M2">
-        <v>152805</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3">
-        <v>1172</v>
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F3">
         <v>45.28</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3">
         <v>1.66</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>75.16</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.8</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>81.5</v>
       </c>
-      <c r="K3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
+      <c r="L3" t="s">
+        <v>73</v>
       </c>
       <c r="M3">
-        <v>153230</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>1147</v>
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F4">
         <v>56.43</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4">
         <v>1.66</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>93.67</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.8</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>101.57</v>
       </c>
-      <c r="K4" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+      <c r="L4" t="s">
+        <v>74</v>
       </c>
       <c r="M4">
-        <v>175996</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5">
-        <v>1148</v>
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F5">
         <v>38.89</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5">
         <v>1.66</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>64.56</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.8</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>70</v>
       </c>
-      <c r="K5" t="s">
-        <v>47</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
+      <c r="L5" t="s">
+        <v>75</v>
       </c>
       <c r="M5">
-        <v>202123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>1911</v>
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F6">
         <v>18.25</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6">
         <v>1.66</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>30.3</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.8</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>32.85</v>
       </c>
-      <c r="K6" t="s">
-        <v>48</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+      <c r="L6" t="s">
+        <v>76</v>
       </c>
       <c r="M6">
-        <v>173826</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7">
-        <v>1911</v>
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="F7">
         <v>19.24</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7">
         <v>1.43</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>27.51</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.52</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>29.24</v>
       </c>
-      <c r="K7" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
+      <c r="L7" t="s">
+        <v>77</v>
       </c>
       <c r="M7">
-        <v>173949</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8">
-        <v>1911</v>
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8">
+        <v>1.66</v>
+      </c>
+      <c r="I8" s="1">
+        <v>166</v>
+      </c>
+      <c r="J8">
+        <v>1.8</v>
+      </c>
+      <c r="K8" s="1">
+        <v>180</v>
+      </c>
+      <c r="L8" t="s">
+        <v>78</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
         <v>36</v>
       </c>
-      <c r="E8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8">
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9">
         <v>61.04</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9">
         <v>1.66</v>
       </c>
-      <c r="H8">
+      <c r="I9" s="1">
         <v>101.33</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J9">
         <v>1.8</v>
       </c>
-      <c r="J8">
+      <c r="K9" s="1">
         <v>109.87</v>
       </c>
-      <c r="K8" t="s">
-        <v>50</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>103572</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9">
-        <v>1911</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9">
-        <v>100</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1.66</v>
-      </c>
-      <c r="H9">
-        <v>166</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J9">
-        <v>180</v>
-      </c>
-      <c r="K9" t="s">
-        <v>51</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
+      <c r="L9" t="s">
+        <v>79</v>
       </c>
       <c r="M9">
-        <v>174283</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10">
-        <v>1172</v>
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F10">
         <v>57.18</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10">
         <v>1.66</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>94.92</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.8</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>102.92</v>
       </c>
-      <c r="K10" t="s">
-        <v>52</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="L10" t="s">
+        <v>80</v>
       </c>
       <c r="M10">
-        <v>155760</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11">
-        <v>1148</v>
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F11">
         <v>102.8</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11">
         <v>1.65</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>169.62</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.79</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>184.01</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
+        <v>81</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
         <v>53</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>203568</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12">
-        <v>1172</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F12">
         <v>52.25</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12">
         <v>1.65</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>86.20999999999999</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.79</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>93.53</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
+        <v>82</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
         <v>54</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>155930</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13">
-        <v>1147</v>
-      </c>
-      <c r="C13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" t="s">
-        <v>33</v>
-      </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F13">
         <v>48.79</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13">
         <v>1.65</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>80.5</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.79</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>87.33</v>
       </c>
-      <c r="K13" t="s">
-        <v>55</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
+      <c r="L13" t="s">
+        <v>83</v>
       </c>
       <c r="M13">
-        <v>179406</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14">
-        <v>1148</v>
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F14">
         <v>100</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14">
         <v>1.65</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>165</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>1.79</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>179</v>
       </c>
-      <c r="K14" t="s">
-        <v>56</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
+      <c r="L14" t="s">
+        <v>84</v>
       </c>
       <c r="M14">
-        <v>204393</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15">
-        <v>1172</v>
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F15">
         <v>109.13</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15">
         <v>1.65</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="1">
         <v>180.06</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>1.79</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>195.34</v>
       </c>
-      <c r="K15" t="s">
-        <v>57</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
+      <c r="L15" t="s">
+        <v>85</v>
       </c>
       <c r="M15">
-        <v>157547</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16">
-        <v>1147</v>
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="F16">
         <v>25.3</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16">
         <v>1.47</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="1">
         <v>37.19</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>1.54</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>38.96</v>
       </c>
-      <c r="K16" t="s">
-        <v>58</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
+      <c r="L16" t="s">
+        <v>86</v>
       </c>
       <c r="M16">
-        <v>180318</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17">
-        <v>1148</v>
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F17">
         <v>50.04</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" t="s">
+        <v>71</v>
+      </c>
+      <c r="H17">
         <v>1.65</v>
       </c>
-      <c r="H17">
+      <c r="I17" s="1">
         <v>82.56999999999999</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17">
         <v>1.79</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="1">
         <v>89.56999999999999</v>
       </c>
-      <c r="K17" t="s">
-        <v>59</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
+      <c r="L17" t="s">
+        <v>87</v>
       </c>
       <c r="M17">
-        <v>204927</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18">
-        <v>1179</v>
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F18">
         <v>59.11</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18">
         <v>1.65</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="1">
         <v>97.53</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18">
         <v>1.77</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="1">
         <v>104.62</v>
       </c>
-      <c r="K18" t="s">
-        <v>60</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
+      <c r="L18" t="s">
+        <v>88</v>
       </c>
       <c r="M18">
-        <v>243614</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19">
-        <v>1179</v>
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="F19">
         <v>9.58</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19">
         <v>1.47</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="1">
         <v>14.08</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>1.54</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>14.75</v>
       </c>
-      <c r="K19" t="s">
-        <v>60</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
+      <c r="L19" t="s">
+        <v>88</v>
       </c>
       <c r="M19">
-        <v>243614</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20">
-        <v>1148</v>
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F20">
         <v>100</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" t="s">
+        <v>71</v>
+      </c>
+      <c r="H20">
         <v>1.64</v>
       </c>
-      <c r="H20">
+      <c r="I20" s="1">
         <v>164</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20">
         <v>1.77</v>
       </c>
-      <c r="J20">
+      <c r="K20" s="1">
         <v>177</v>
       </c>
-      <c r="K20" t="s">
-        <v>61</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
+      <c r="L20" t="s">
+        <v>89</v>
       </c>
       <c r="M20">
-        <v>206176</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21">
-        <v>1172</v>
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F21">
         <v>50.34</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21">
         <v>1.64</v>
       </c>
-      <c r="H21">
+      <c r="I21" s="1">
         <v>82.56</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21">
         <v>1.76</v>
       </c>
-      <c r="J21">
+      <c r="K21" s="1">
         <v>88.59999999999999</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
+        <v>90</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="G22" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22">
+        <v>1.64</v>
+      </c>
+      <c r="I22" s="1">
+        <v>105.44</v>
+      </c>
+      <c r="J22">
+        <v>1.75</v>
+      </c>
+      <c r="K22" s="1">
+        <v>112.51</v>
+      </c>
+      <c r="L22" t="s">
+        <v>91</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23">
+        <v>18.94</v>
+      </c>
+      <c r="G23" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23">
+        <v>0.79</v>
+      </c>
+      <c r="I23" s="1">
+        <v>14.96</v>
+      </c>
+      <c r="J23">
+        <v>0.79</v>
+      </c>
+      <c r="K23" s="1">
+        <v>14.96</v>
+      </c>
+      <c r="L23" t="s">
+        <v>92</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" t="s">
         <v>62</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>159164</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="3" t="s">
+      <c r="E24" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="G24" t="s">
+        <v>71</v>
+      </c>
+      <c r="H24">
+        <v>1.63</v>
+      </c>
+      <c r="I24" s="1">
+        <v>109.19</v>
+      </c>
+      <c r="J24">
+        <v>1.75</v>
+      </c>
+      <c r="K24" s="1">
+        <v>117.23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>93</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25">
+        <v>65</v>
+      </c>
+      <c r="G25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25">
+        <v>1.63</v>
+      </c>
+      <c r="I25" s="1">
+        <v>105.95</v>
+      </c>
+      <c r="J25">
+        <v>1.75</v>
+      </c>
+      <c r="K25" s="1">
+        <v>113.75</v>
+      </c>
+      <c r="L25" t="s">
+        <v>94</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26">
+        <v>77.22</v>
+      </c>
+      <c r="G26" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26">
+        <v>1.63</v>
+      </c>
+      <c r="I26" s="1">
+        <v>125.87</v>
+      </c>
+      <c r="J26">
+        <v>1.75</v>
+      </c>
+      <c r="K26" s="1">
+        <v>135.14</v>
+      </c>
+      <c r="L26" t="s">
+        <v>95</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27">
+        <v>64</v>
+      </c>
+      <c r="G27" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27">
+        <v>1.63</v>
+      </c>
+      <c r="I27" s="1">
+        <v>104.32</v>
+      </c>
+      <c r="J27">
+        <v>1.75</v>
+      </c>
+      <c r="K27" s="1">
+        <v>112</v>
+      </c>
+      <c r="L27" t="s">
+        <v>96</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28">
+        <v>55.79</v>
+      </c>
+      <c r="G28" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28">
+        <v>1.63</v>
+      </c>
+      <c r="I28" s="1">
+        <v>90.94</v>
+      </c>
+      <c r="J28">
+        <v>1.75</v>
+      </c>
+      <c r="K28" s="1">
+        <v>97.63</v>
+      </c>
+      <c r="L28" t="s">
+        <v>97</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="4" t="s">
+      <c r="E29" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29">
+        <v>35.37</v>
+      </c>
+      <c r="G29" t="s">
+        <v>71</v>
+      </c>
+      <c r="H29">
+        <v>0.79</v>
+      </c>
+      <c r="I29" s="1">
+        <v>27.94</v>
+      </c>
+      <c r="J29">
+        <v>0.79</v>
+      </c>
+      <c r="K29" s="1">
+        <v>27.94</v>
+      </c>
+      <c r="L29" t="s">
+        <v>98</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30">
+        <v>100</v>
+      </c>
+      <c r="G30" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30">
+        <v>1.63</v>
+      </c>
+      <c r="I30" s="1">
+        <v>163</v>
+      </c>
+      <c r="J30">
+        <v>1.72</v>
+      </c>
+      <c r="K30" s="1">
+        <v>172</v>
+      </c>
+      <c r="L30" t="s">
+        <v>99</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" t="s">
+        <v>67</v>
+      </c>
+      <c r="F31">
+        <v>40</v>
+      </c>
+      <c r="G31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H31">
+        <v>1.63</v>
+      </c>
+      <c r="I31" s="1">
+        <v>65.2</v>
+      </c>
+      <c r="J31">
+        <v>1.72</v>
+      </c>
+      <c r="K31" s="1">
+        <v>68.8</v>
+      </c>
+      <c r="L31" t="s">
+        <v>100</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" t="s">
+        <v>67</v>
+      </c>
+      <c r="F32">
+        <v>100</v>
+      </c>
+      <c r="G32" t="s">
+        <v>71</v>
+      </c>
+      <c r="H32">
+        <v>1.63</v>
+      </c>
+      <c r="I32" s="1">
+        <v>163</v>
+      </c>
+      <c r="J32">
+        <v>1.72</v>
+      </c>
+      <c r="K32" s="1">
+        <v>172</v>
+      </c>
+      <c r="L32" t="s">
+        <v>101</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" t="s">
+        <v>67</v>
+      </c>
+      <c r="F33">
+        <v>39.67</v>
+      </c>
+      <c r="G33" t="s">
+        <v>71</v>
+      </c>
+      <c r="H33">
+        <v>1.63</v>
+      </c>
+      <c r="I33" s="1">
+        <v>64.66</v>
+      </c>
+      <c r="J33">
+        <v>1.72</v>
+      </c>
+      <c r="K33" s="1">
+        <v>68.23</v>
+      </c>
+      <c r="L33" t="s">
+        <v>102</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" t="s">
+        <v>66</v>
+      </c>
+      <c r="E34" t="s">
+        <v>67</v>
+      </c>
+      <c r="F34">
+        <v>45.29</v>
+      </c>
+      <c r="G34" t="s">
+        <v>71</v>
+      </c>
+      <c r="H34">
+        <v>1.63</v>
+      </c>
+      <c r="I34" s="1">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="J34">
+        <v>1.72</v>
+      </c>
+      <c r="K34" s="1">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="L34" t="s">
+        <v>103</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" t="s">
+        <v>63</v>
+      </c>
+      <c r="E35" t="s">
+        <v>69</v>
+      </c>
+      <c r="F35">
+        <v>26.2</v>
+      </c>
+      <c r="G35" t="s">
+        <v>71</v>
+      </c>
+      <c r="H35">
+        <v>0.77</v>
+      </c>
+      <c r="I35" s="1">
+        <v>20.17</v>
+      </c>
+      <c r="J35">
+        <v>0.77</v>
+      </c>
+      <c r="K35" s="1">
+        <v>20.17</v>
+      </c>
+      <c r="L35" t="s">
+        <v>104</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="6">
-        <v>1100.24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>17</v>
-      </c>
-      <c r="D26" s="7">
-        <v>1.6525</v>
-      </c>
-      <c r="E26" s="6">
-        <v>1818.17</v>
-      </c>
-      <c r="F26" s="6">
-        <v>1968.99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="6">
-        <v>54.12</v>
-      </c>
-      <c r="C27" s="6">
+      <c r="E36" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36">
+        <v>7.46</v>
+      </c>
+      <c r="G36" t="s">
+        <v>71</v>
+      </c>
+      <c r="H36">
+        <v>1.82</v>
+      </c>
+      <c r="I36" s="1">
+        <v>13.58</v>
+      </c>
+      <c r="J36">
+        <v>1.82</v>
+      </c>
+      <c r="K36" s="1">
+        <v>13.58</v>
+      </c>
+      <c r="L36" t="s">
+        <v>105</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" t="s">
+        <v>68</v>
+      </c>
+      <c r="F37">
+        <v>18.46</v>
+      </c>
+      <c r="G37" t="s">
+        <v>71</v>
+      </c>
+      <c r="H37">
+        <v>1.5</v>
+      </c>
+      <c r="I37" s="1">
+        <v>27.69</v>
+      </c>
+      <c r="J37">
+        <v>1.57</v>
+      </c>
+      <c r="K37" s="1">
+        <v>28.98</v>
+      </c>
+      <c r="L37" t="s">
+        <v>97</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" t="s">
+        <v>67</v>
+      </c>
+      <c r="F38">
+        <v>78.22</v>
+      </c>
+      <c r="G38" t="s">
+        <v>71</v>
+      </c>
+      <c r="H38">
+        <v>1.63</v>
+      </c>
+      <c r="I38" s="1">
+        <v>127.5</v>
+      </c>
+      <c r="J38">
+        <v>1.72</v>
+      </c>
+      <c r="K38" s="1">
+        <v>134.54</v>
+      </c>
+      <c r="L38" t="s">
+        <v>106</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" t="s">
+        <v>67</v>
+      </c>
+      <c r="F39">
+        <v>62.06</v>
+      </c>
+      <c r="G39" t="s">
+        <v>71</v>
+      </c>
+      <c r="H39">
+        <v>1.63</v>
+      </c>
+      <c r="I39" s="1">
+        <v>101.16</v>
+      </c>
+      <c r="J39">
+        <v>1.71</v>
+      </c>
+      <c r="K39" s="1">
+        <v>106.12</v>
+      </c>
+      <c r="L39" t="s">
+        <v>107</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" t="s">
+        <v>67</v>
+      </c>
+      <c r="F40">
+        <v>62.2</v>
+      </c>
+      <c r="G40" t="s">
+        <v>71</v>
+      </c>
+      <c r="H40">
+        <v>1.62</v>
+      </c>
+      <c r="I40" s="1">
+        <v>100.76</v>
+      </c>
+      <c r="J40">
+        <v>1.7</v>
+      </c>
+      <c r="K40" s="1">
+        <v>105.74</v>
+      </c>
+      <c r="L40" t="s">
+        <v>108</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" t="s">
+        <v>67</v>
+      </c>
+      <c r="F41">
+        <v>70.26000000000001</v>
+      </c>
+      <c r="G41" t="s">
+        <v>71</v>
+      </c>
+      <c r="H41">
+        <v>1.62</v>
+      </c>
+      <c r="I41" s="1">
+        <v>113.82</v>
+      </c>
+      <c r="J41">
+        <v>1.7</v>
+      </c>
+      <c r="K41" s="1">
+        <v>119.44</v>
+      </c>
+      <c r="L41" t="s">
+        <v>109</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" t="s">
+        <v>68</v>
+      </c>
+      <c r="F42">
+        <v>28.71</v>
+      </c>
+      <c r="G42" t="s">
+        <v>71</v>
+      </c>
+      <c r="H42">
+        <v>1.52</v>
+      </c>
+      <c r="I42" s="1">
+        <v>43.64</v>
+      </c>
+      <c r="J42">
+        <v>1.57</v>
+      </c>
+      <c r="K42" s="1">
+        <v>45.07</v>
+      </c>
+      <c r="L42" t="s">
+        <v>110</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="6">
+        <v>2091.23</v>
+      </c>
+      <c r="C47" s="6">
+        <v>32</v>
+      </c>
+      <c r="D47" s="7">
+        <v>1.6415</v>
+      </c>
+      <c r="E47" s="6">
+        <v>3432.8</v>
+      </c>
+      <c r="F47" s="6">
+        <v>3682.02</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B48" s="6">
+        <v>101.29</v>
+      </c>
+      <c r="C48" s="6">
+        <v>5</v>
+      </c>
+      <c r="D48" s="7">
+        <v>1.482</v>
+      </c>
+      <c r="E48" s="6">
+        <v>150.11</v>
+      </c>
+      <c r="F48" s="6">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B49" s="6">
+        <v>80.51000000000001</v>
+      </c>
+      <c r="C49" s="6">
         <v>3</v>
       </c>
-      <c r="D27" s="7">
-        <v>1.4557</v>
-      </c>
-      <c r="E27" s="6">
-        <v>78.78</v>
-      </c>
-      <c r="F27" s="6">
-        <v>82.95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="9">
-        <v>1154.36</v>
-      </c>
-      <c r="C28" s="9">
-        <v>20</v>
-      </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="9">
-        <v>1896.95</v>
-      </c>
-      <c r="F28" s="9">
-        <v>2051.94</v>
+      <c r="D49" s="7">
+        <v>0.7834</v>
+      </c>
+      <c r="E49" s="6">
+        <v>63.07</v>
+      </c>
+      <c r="F49" s="6">
+        <v>63.07</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" s="6">
+        <v>7.46</v>
+      </c>
+      <c r="C50" s="6">
+        <v>1</v>
+      </c>
+      <c r="D50" s="7">
+        <v>1.8204</v>
+      </c>
+      <c r="E50" s="6">
+        <v>13.58</v>
+      </c>
+      <c r="F50" s="6">
+        <v>13.58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B51" s="9">
+        <v>2280.49</v>
+      </c>
+      <c r="C51" s="9">
+        <v>41</v>
+      </c>
+      <c r="D51" s="7"/>
+      <c r="E51" s="9">
+        <v>3659.56</v>
+      </c>
+      <c r="F51" s="9">
+        <v>3915.67</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A45:F45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ПОДИ ЕООД/ПОДИ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ПОДИ ЕООД/ПОДИ ЕООД.xlsx
@@ -520,7 +520,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -530,12 +530,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,17 +579,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ПОДИ ЕООД/ПОДИ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ПОДИ ЕООД/ПОДИ ЕООД.xlsx
@@ -487,7 +487,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -2962,7 +2962,7 @@
         <v>28</v>
       </c>
       <c r="D51" s="7">
-        <v>1.5309</v>
+        <v>1.53087</v>
       </c>
       <c r="E51" s="6">
         <v>2614.94</v>
@@ -2982,7 +2982,7 @@
         <v>12</v>
       </c>
       <c r="D52" s="7">
-        <v>1.4214</v>
+        <v>1.421406</v>
       </c>
       <c r="E52" s="6">
         <v>256.45</v>
@@ -3002,7 +3002,7 @@
         <v>4</v>
       </c>
       <c r="D53" s="7">
-        <v>0.6449</v>
+        <v>0.644909</v>
       </c>
       <c r="E53" s="6">
         <v>74.3</v>
@@ -3022,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="D54" s="7">
-        <v>1.7898</v>
+        <v>1.789786</v>
       </c>
       <c r="E54" s="6">
         <v>15.07</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ПОДИ ЕООД/ПОДИ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ПОДИ ЕООД/ПОДИ ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="155">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -489,8 +486,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -583,10 +580,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -881,7 +878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -894,13 +891,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -943,2128 +940,1990 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F2">
         <v>28.485</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H2">
         <v>0.66</v>
       </c>
       <c r="I2" s="1">
+        <v>18.8</v>
+      </c>
+      <c r="J2">
         <v>0.66</v>
       </c>
-      <c r="J2">
-        <v>18.8001</v>
-      </c>
       <c r="K2" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="L2" s="1">
-        <v>18.8001</v>
-      </c>
-      <c r="M2" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>18.8</v>
+      </c>
+      <c r="L2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F3">
         <v>13.333</v>
       </c>
       <c r="G3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H3">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I3" s="1">
-        <v>1.389</v>
+        <v>18.52</v>
       </c>
       <c r="J3">
-        <v>18.519537</v>
+        <v>1.5</v>
       </c>
       <c r="K3" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L3" s="1">
-        <v>19.9995</v>
-      </c>
-      <c r="M3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F4">
         <v>100.351</v>
       </c>
       <c r="G4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H4">
-        <v>1.399</v>
+        <v>1.429</v>
       </c>
       <c r="I4" s="1">
-        <v>1.429</v>
+        <v>143.402</v>
       </c>
       <c r="J4">
-        <v>143.401579</v>
+        <v>1.51</v>
       </c>
       <c r="K4" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L4" s="1">
-        <v>151.53001</v>
-      </c>
-      <c r="M4" t="s">
-        <v>73</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>151.53</v>
+      </c>
+      <c r="L4" t="s">
+        <v>72</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F5">
         <v>4.42</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H5">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I5" s="1">
-        <v>1.389</v>
+        <v>6.139</v>
       </c>
       <c r="J5">
-        <v>6.13938</v>
+        <v>1.5</v>
       </c>
       <c r="K5" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L5" s="1">
         <v>6.63</v>
       </c>
-      <c r="M5" t="s">
-        <v>74</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="L5" t="s">
+        <v>73</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F6">
         <v>22.331</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H6">
-        <v>1.399</v>
+        <v>1.429</v>
       </c>
       <c r="I6" s="1">
-        <v>1.429</v>
+        <v>31.911</v>
       </c>
       <c r="J6">
-        <v>31.910999</v>
+        <v>1.51</v>
       </c>
       <c r="K6" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L6" s="1">
-        <v>33.71981</v>
-      </c>
-      <c r="M6" t="s">
-        <v>75</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>33.72</v>
+      </c>
+      <c r="L6" t="s">
+        <v>74</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F7">
         <v>17.093</v>
       </c>
       <c r="G7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H7">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I7" s="1">
-        <v>1.389</v>
+        <v>23.742</v>
       </c>
       <c r="J7">
-        <v>23.742177</v>
+        <v>1.5</v>
       </c>
       <c r="K7" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L7" s="1">
-        <v>25.6395</v>
-      </c>
-      <c r="M7" t="s">
-        <v>76</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>25.64</v>
+      </c>
+      <c r="L7" t="s">
+        <v>75</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F8">
         <v>49.342</v>
       </c>
       <c r="G8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H8">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I8" s="1">
-        <v>1.436</v>
+        <v>70.855</v>
       </c>
       <c r="J8">
-        <v>70.85511200000001</v>
+        <v>1.52</v>
       </c>
       <c r="K8" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L8" s="1">
-        <v>74.99984000000001</v>
-      </c>
-      <c r="M8" t="s">
-        <v>77</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>75</v>
+      </c>
+      <c r="L8" t="s">
+        <v>76</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F9">
         <v>93.63800000000001</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H9">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I9" s="1">
-        <v>1.436</v>
+        <v>134.464</v>
       </c>
       <c r="J9">
-        <v>134.464168</v>
+        <v>1.52</v>
       </c>
       <c r="K9" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L9" s="1">
-        <v>142.32976</v>
-      </c>
-      <c r="M9" t="s">
-        <v>78</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>142.33</v>
+      </c>
+      <c r="L9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F10">
         <v>9.82</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H10">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I10" s="1">
-        <v>1.389</v>
+        <v>13.64</v>
       </c>
       <c r="J10">
-        <v>13.63998</v>
+        <v>1.5</v>
       </c>
       <c r="K10" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L10" s="1">
         <v>14.73</v>
       </c>
-      <c r="M10" t="s">
-        <v>78</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="L10" t="s">
+        <v>77</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F11">
         <v>47.368</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H11">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I11" s="1">
-        <v>1.442</v>
+        <v>68.30500000000001</v>
       </c>
       <c r="J11">
-        <v>68.30465599999999</v>
+        <v>1.52</v>
       </c>
       <c r="K11" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L11" s="1">
-        <v>71.99936</v>
-      </c>
-      <c r="M11" t="s">
-        <v>79</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>71.999</v>
+      </c>
+      <c r="L11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F12">
         <v>63.487</v>
       </c>
       <c r="G12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H12">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I12" s="1">
-        <v>1.442</v>
+        <v>91.548</v>
       </c>
       <c r="J12">
-        <v>91.548254</v>
+        <v>1.52</v>
       </c>
       <c r="K12" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L12" s="1">
-        <v>96.50024000000001</v>
-      </c>
-      <c r="M12" t="s">
-        <v>80</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>96.5</v>
+      </c>
+      <c r="L12" t="s">
+        <v>79</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F13">
         <v>9.423</v>
       </c>
       <c r="G13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H13">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I13" s="1">
-        <v>1.389</v>
+        <v>13.089</v>
       </c>
       <c r="J13">
-        <v>13.088547</v>
+        <v>1.49</v>
       </c>
       <c r="K13" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L13" s="1">
-        <v>14.04027</v>
-      </c>
-      <c r="M13" t="s">
-        <v>80</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>14.04</v>
+      </c>
+      <c r="L13" t="s">
+        <v>79</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F14">
         <v>28.087</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H14">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I14" s="1">
-        <v>1.389</v>
+        <v>39.013</v>
       </c>
       <c r="J14">
-        <v>39.012843</v>
+        <v>1.49</v>
       </c>
       <c r="K14" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L14" s="1">
-        <v>41.84963</v>
-      </c>
-      <c r="M14" t="s">
-        <v>81</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>41.85</v>
+      </c>
+      <c r="L14" t="s">
+        <v>80</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H15">
-        <v>1.437</v>
+        <v>1.467</v>
       </c>
       <c r="I15" s="1">
-        <v>1.467</v>
+        <v>7.335</v>
       </c>
       <c r="J15">
-        <v>7.335</v>
+        <v>1.54</v>
       </c>
       <c r="K15" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L15" s="1">
         <v>7.7</v>
       </c>
-      <c r="M15" t="s">
-        <v>82</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="L15" t="s">
+        <v>81</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F16">
         <v>136.312</v>
       </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H16">
-        <v>1.437</v>
+        <v>1.467</v>
       </c>
       <c r="I16" s="1">
-        <v>1.467</v>
+        <v>199.97</v>
       </c>
       <c r="J16">
-        <v>199.969704</v>
+        <v>1.54</v>
       </c>
       <c r="K16" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L16" s="1">
-        <v>209.92048</v>
-      </c>
-      <c r="M16" t="s">
-        <v>83</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>209.92</v>
+      </c>
+      <c r="L16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F17">
         <v>46.053</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H17">
-        <v>1.437</v>
+        <v>1.467</v>
       </c>
       <c r="I17" s="1">
-        <v>1.467</v>
+        <v>67.56</v>
       </c>
       <c r="J17">
-        <v>67.55975100000001</v>
+        <v>1.52</v>
       </c>
       <c r="K17" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L17" s="1">
-        <v>70.00055999999999</v>
-      </c>
-      <c r="M17" t="s">
-        <v>84</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>70.001</v>
+      </c>
+      <c r="L17" t="s">
+        <v>83</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F18">
         <v>50.188</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H18">
-        <v>1.437</v>
+        <v>1.467</v>
       </c>
       <c r="I18" s="1">
-        <v>1.467</v>
+        <v>73.626</v>
       </c>
       <c r="J18">
-        <v>73.62579599999999</v>
+        <v>1.54</v>
       </c>
       <c r="K18" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L18" s="1">
-        <v>77.28952</v>
-      </c>
-      <c r="M18" t="s">
-        <v>85</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>77.29000000000001</v>
+      </c>
+      <c r="L18" t="s">
+        <v>84</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F19">
         <v>126.122</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H19">
-        <v>1.451</v>
+        <v>1.481</v>
       </c>
       <c r="I19" s="1">
-        <v>1.481</v>
+        <v>186.787</v>
       </c>
       <c r="J19">
-        <v>186.786682</v>
+        <v>1.56</v>
       </c>
       <c r="K19" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L19" s="1">
-        <v>196.75032</v>
-      </c>
-      <c r="M19" t="s">
-        <v>86</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>196.75</v>
+      </c>
+      <c r="L19" t="s">
+        <v>85</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F20">
         <v>57.487</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H20">
-        <v>1.451</v>
+        <v>1.481</v>
       </c>
       <c r="I20" s="1">
-        <v>1.481</v>
+        <v>85.13800000000001</v>
       </c>
       <c r="J20">
-        <v>85.13824700000001</v>
+        <v>1.56</v>
       </c>
       <c r="K20" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L20" s="1">
-        <v>89.67972</v>
-      </c>
-      <c r="M20" t="s">
-        <v>87</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+        <v>89.68000000000001</v>
+      </c>
+      <c r="L20" t="s">
+        <v>86</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F21">
         <v>9.483000000000001</v>
       </c>
       <c r="G21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H21">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I21" s="1">
-        <v>1.389</v>
+        <v>13.172</v>
       </c>
       <c r="J21">
-        <v>13.171887</v>
+        <v>1.49</v>
       </c>
       <c r="K21" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L21" s="1">
-        <v>14.12967</v>
-      </c>
-      <c r="M21" t="s">
-        <v>87</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>14.13</v>
+      </c>
+      <c r="L21" t="s">
+        <v>86</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F22">
         <v>38.462</v>
       </c>
       <c r="G22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H22">
-        <v>1.451</v>
+        <v>1.481</v>
       </c>
       <c r="I22" s="1">
-        <v>1.481</v>
+        <v>56.962</v>
       </c>
       <c r="J22">
-        <v>56.962222</v>
+        <v>1.56</v>
       </c>
       <c r="K22" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L22" s="1">
-        <v>60.00072</v>
-      </c>
-      <c r="M22" t="s">
-        <v>88</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>60.001</v>
+      </c>
+      <c r="L22" t="s">
+        <v>87</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F23">
         <v>59.41</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H23">
-        <v>1.469</v>
+        <v>1.499</v>
       </c>
       <c r="I23" s="1">
-        <v>1.499</v>
+        <v>89.056</v>
       </c>
       <c r="J23">
-        <v>89.05559</v>
+        <v>1.56</v>
       </c>
       <c r="K23" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L23" s="1">
-        <v>92.67959999999999</v>
-      </c>
-      <c r="M23" t="s">
-        <v>89</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="L23" t="s">
+        <v>88</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F24">
         <v>37.108</v>
       </c>
       <c r="G24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H24">
-        <v>1.489</v>
+        <v>1.519</v>
       </c>
       <c r="I24" s="1">
-        <v>1.519</v>
+        <v>56.367</v>
       </c>
       <c r="J24">
-        <v>56.367052</v>
+        <v>1.58</v>
       </c>
       <c r="K24" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L24" s="1">
-        <v>58.63064</v>
-      </c>
-      <c r="M24" t="s">
-        <v>90</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>58.631</v>
+      </c>
+      <c r="L24" t="s">
+        <v>89</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F25">
         <v>62.987</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H25">
-        <v>1.489</v>
+        <v>1.519</v>
       </c>
       <c r="I25" s="1">
-        <v>1.519</v>
+        <v>95.67700000000001</v>
       </c>
       <c r="J25">
-        <v>95.67725299999999</v>
+        <v>1.58</v>
       </c>
       <c r="K25" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L25" s="1">
-        <v>99.51946</v>
-      </c>
-      <c r="M25" t="s">
-        <v>91</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>99.51900000000001</v>
+      </c>
+      <c r="L25" t="s">
+        <v>90</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F26">
         <v>76.062</v>
       </c>
       <c r="G26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H26">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I26" s="1">
-        <v>1.529</v>
+        <v>116.299</v>
       </c>
       <c r="J26">
-        <v>116.298798</v>
+        <v>1.61</v>
       </c>
       <c r="K26" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L26" s="1">
-        <v>122.45982</v>
-      </c>
-      <c r="M26" t="s">
-        <v>92</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>122.46</v>
+      </c>
+      <c r="L26" t="s">
+        <v>91</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F27">
         <v>34.663</v>
       </c>
       <c r="G27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H27">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I27" s="1">
-        <v>1.529</v>
+        <v>53</v>
       </c>
       <c r="J27">
-        <v>52.999727</v>
+        <v>1.63</v>
       </c>
       <c r="K27" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L27" s="1">
-        <v>56.50069</v>
-      </c>
-      <c r="M27" t="s">
-        <v>93</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+        <v>56.501</v>
+      </c>
+      <c r="L27" t="s">
+        <v>92</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F28">
         <v>100</v>
       </c>
       <c r="G28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H28">
-        <v>1.546</v>
+        <v>1.576</v>
       </c>
       <c r="I28" s="1">
-        <v>1.576</v>
+        <v>157.6</v>
       </c>
       <c r="J28">
-        <v>157.6</v>
+        <v>1.68</v>
       </c>
       <c r="K28" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L28" s="1">
         <v>168</v>
       </c>
-      <c r="M28" t="s">
-        <v>94</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="L28" t="s">
+        <v>93</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F29">
         <v>28.016</v>
       </c>
       <c r="G29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H29">
         <v>0.64</v>
       </c>
       <c r="I29" s="1">
+        <v>17.93</v>
+      </c>
+      <c r="J29">
         <v>0.64</v>
       </c>
-      <c r="J29">
-        <v>17.93024</v>
-      </c>
       <c r="K29" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L29" s="1">
-        <v>17.93024</v>
-      </c>
-      <c r="M29" t="s">
-        <v>95</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+        <v>17.93</v>
+      </c>
+      <c r="L29" t="s">
+        <v>94</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F30">
         <v>8.419</v>
       </c>
       <c r="G30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H30">
         <v>1.79</v>
       </c>
       <c r="I30" s="1">
+        <v>15.07</v>
+      </c>
+      <c r="J30">
         <v>1.79</v>
       </c>
-      <c r="J30">
-        <v>15.07001</v>
-      </c>
       <c r="K30" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="L30" s="1">
-        <v>15.07001</v>
-      </c>
-      <c r="M30" t="s">
-        <v>96</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+        <v>15.07</v>
+      </c>
+      <c r="L30" t="s">
+        <v>95</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F31">
         <v>69.488</v>
       </c>
       <c r="G31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H31">
-        <v>1.546</v>
+        <v>1.576</v>
       </c>
       <c r="I31" s="1">
-        <v>1.576</v>
+        <v>109.513</v>
       </c>
       <c r="J31">
-        <v>109.513088</v>
+        <v>1.68</v>
       </c>
       <c r="K31" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L31" s="1">
-        <v>116.73984</v>
-      </c>
-      <c r="M31" t="s">
-        <v>97</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+        <v>116.74</v>
+      </c>
+      <c r="L31" t="s">
+        <v>96</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F32">
         <v>66.952</v>
       </c>
       <c r="G32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H32">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I32" s="1">
-        <v>1.594</v>
+        <v>106.721</v>
       </c>
       <c r="J32">
-        <v>106.721488</v>
+        <v>1.68</v>
       </c>
       <c r="K32" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L32" s="1">
-        <v>112.47936</v>
-      </c>
-      <c r="M32" t="s">
-        <v>98</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+        <v>112.479</v>
+      </c>
+      <c r="L32" t="s">
+        <v>97</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F33">
         <v>56.16</v>
       </c>
       <c r="G33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H33">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I33" s="1">
-        <v>1.618</v>
+        <v>90.867</v>
       </c>
       <c r="J33">
-        <v>90.86687999999999</v>
+        <v>1.69</v>
       </c>
       <c r="K33" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L33" s="1">
-        <v>94.9104</v>
-      </c>
-      <c r="M33" t="s">
-        <v>99</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+        <v>94.91</v>
+      </c>
+      <c r="L33" t="s">
+        <v>98</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F34">
         <v>9.143000000000001</v>
       </c>
       <c r="G34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H34">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I34" s="1">
-        <v>1.441</v>
+        <v>13.175</v>
       </c>
       <c r="J34">
-        <v>13.175063</v>
+        <v>1.54</v>
       </c>
       <c r="K34" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L34" s="1">
-        <v>14.08022</v>
-      </c>
-      <c r="M34" t="s">
-        <v>99</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+        <v>14.08</v>
+      </c>
+      <c r="L34" t="s">
+        <v>98</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F35">
         <v>35.3</v>
       </c>
       <c r="G35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H35">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I35" s="1">
-        <v>1.618</v>
+        <v>57.115</v>
       </c>
       <c r="J35">
-        <v>57.1154</v>
+        <v>1.7</v>
       </c>
       <c r="K35" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L35" s="1">
         <v>60.01</v>
       </c>
-      <c r="M35" t="s">
-        <v>100</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="L35" t="s">
+        <v>99</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F36">
         <v>44.448</v>
       </c>
       <c r="G36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H36">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I36" s="1">
-        <v>1.649</v>
+        <v>73.295</v>
       </c>
       <c r="J36">
-        <v>73.294752</v>
+        <v>1.74</v>
       </c>
       <c r="K36" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L36" s="1">
-        <v>77.33951999999999</v>
-      </c>
-      <c r="M36" t="s">
-        <v>101</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+        <v>77.34</v>
+      </c>
+      <c r="L36" t="s">
+        <v>100</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F37">
         <v>23.013</v>
       </c>
       <c r="G37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H37">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I37" s="1">
-        <v>1.441</v>
+        <v>33.162</v>
       </c>
       <c r="J37">
-        <v>33.161733</v>
+        <v>1.55</v>
       </c>
       <c r="K37" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L37" s="1">
-        <v>35.67015</v>
-      </c>
-      <c r="M37" t="s">
-        <v>102</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+        <v>35.67</v>
+      </c>
+      <c r="L37" t="s">
+        <v>101</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F38">
         <v>30</v>
       </c>
       <c r="G38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H38">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I38" s="1">
-        <v>1.441</v>
+        <v>43.23</v>
       </c>
       <c r="J38">
-        <v>43.23</v>
+        <v>1.55</v>
       </c>
       <c r="K38" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L38" s="1">
         <v>46.5</v>
       </c>
-      <c r="M38" t="s">
-        <v>103</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="L38" t="s">
+        <v>102</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E39" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F39">
         <v>40.24</v>
       </c>
       <c r="G39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H39">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I39" s="1">
-        <v>1.649</v>
+        <v>66.35599999999999</v>
       </c>
       <c r="J39">
-        <v>66.35576</v>
+        <v>1.75</v>
       </c>
       <c r="K39" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L39" s="1">
         <v>70.42</v>
       </c>
-      <c r="M39" t="s">
-        <v>104</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="L39" t="s">
+        <v>103</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F40">
         <v>30.266</v>
       </c>
       <c r="G40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H40">
         <v>0.64</v>
       </c>
       <c r="I40" s="1">
+        <v>19.37</v>
+      </c>
+      <c r="J40">
         <v>0.64</v>
       </c>
-      <c r="J40">
-        <v>19.37024</v>
-      </c>
       <c r="K40" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L40" s="1">
-        <v>19.37024</v>
-      </c>
-      <c r="M40" t="s">
-        <v>95</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+        <v>19.37</v>
+      </c>
+      <c r="L40" t="s">
+        <v>94</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F41">
         <v>9.513</v>
       </c>
       <c r="G41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H41">
-        <v>1.441</v>
+        <v>1.481</v>
       </c>
       <c r="I41" s="1">
-        <v>1.481</v>
+        <v>14.089</v>
       </c>
       <c r="J41">
-        <v>14.088753</v>
+        <v>1.56</v>
       </c>
       <c r="K41" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L41" s="1">
-        <v>14.84028</v>
-      </c>
-      <c r="M41" t="s">
-        <v>98</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+        <v>14.84</v>
+      </c>
+      <c r="L41" t="s">
+        <v>97</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F42">
         <v>17.11</v>
       </c>
       <c r="G42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H42">
-        <v>1.449</v>
+        <v>1.489</v>
       </c>
       <c r="I42" s="1">
-        <v>1.489</v>
+        <v>25.477</v>
       </c>
       <c r="J42">
-        <v>25.47679</v>
+        <v>1.54</v>
       </c>
       <c r="K42" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L42" s="1">
-        <v>26.3494</v>
-      </c>
-      <c r="M42" t="s">
-        <v>105</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+        <v>26.349</v>
+      </c>
+      <c r="L42" t="s">
+        <v>104</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F43">
         <v>105.171</v>
       </c>
       <c r="G43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H43">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I43" s="1">
-        <v>1.704</v>
+        <v>179.211</v>
       </c>
       <c r="J43">
-        <v>179.211384</v>
+        <v>1.75</v>
       </c>
       <c r="K43" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L43" s="1">
-        <v>184.04925</v>
-      </c>
-      <c r="M43" t="s">
-        <v>80</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+        <v>184.049</v>
+      </c>
+      <c r="L43" t="s">
+        <v>79</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" t="s">
         <v>45</v>
       </c>
-      <c r="C44" t="s">
-        <v>46</v>
-      </c>
       <c r="D44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F44">
         <v>28.438</v>
       </c>
       <c r="G44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H44">
         <v>0.64</v>
       </c>
       <c r="I44" s="1">
+        <v>18.2</v>
+      </c>
+      <c r="J44">
         <v>0.64</v>
       </c>
-      <c r="J44">
-        <v>18.20032</v>
-      </c>
       <c r="K44" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L44" s="1">
-        <v>18.20032</v>
-      </c>
-      <c r="M44" t="s">
-        <v>106</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+        <v>18.2</v>
+      </c>
+      <c r="L44" t="s">
+        <v>105</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" t="s">
         <v>37</v>
       </c>
-      <c r="B45" t="s">
-        <v>38</v>
-      </c>
       <c r="C45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F45">
         <v>50.107</v>
       </c>
       <c r="G45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H45">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I45" s="1">
-        <v>1.719</v>
+        <v>86.134</v>
       </c>
       <c r="J45">
-        <v>86.133933</v>
+        <v>1.77</v>
       </c>
       <c r="K45" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L45" s="1">
-        <v>88.68939</v>
-      </c>
-      <c r="M45" t="s">
-        <v>107</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+        <v>88.68899999999999</v>
+      </c>
+      <c r="L45" t="s">
+        <v>106</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" t="s">
         <v>37</v>
       </c>
-      <c r="B46" t="s">
-        <v>38</v>
-      </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F46">
         <v>33.898</v>
       </c>
       <c r="G46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H46">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I46" s="1">
-        <v>1.719</v>
+        <v>58.271</v>
       </c>
       <c r="J46">
-        <v>58.270662</v>
+        <v>1.77</v>
       </c>
       <c r="K46" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L46" s="1">
-        <v>59.99946</v>
-      </c>
-      <c r="M46" t="s">
-        <v>108</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46" t="s">
-        <v>149</v>
+        <v>59.999</v>
+      </c>
+      <c r="L46" t="s">
+        <v>107</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -3074,107 +2933,107 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="C50" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="D50" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>154</v>
-      </c>
       <c r="E50" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B51" s="6">
         <v>1708.135</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="7">
         <v>28</v>
       </c>
       <c r="D51" s="7">
-        <v>1.52994</v>
-      </c>
-      <c r="E51" s="6">
-        <v>2613.34</v>
-      </c>
-      <c r="F51" s="6">
-        <v>2744.85</v>
+        <v>1.53</v>
+      </c>
+      <c r="E51" s="7">
+        <v>2613.345</v>
+      </c>
+      <c r="F51" s="7">
+        <v>2744.848</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B52" s="6">
         <v>180.438</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52" s="7">
         <v>12</v>
       </c>
       <c r="D52" s="7">
-        <v>1.421245</v>
-      </c>
-      <c r="E52" s="6">
-        <v>256.45</v>
-      </c>
-      <c r="F52" s="6">
-        <v>274.46</v>
+        <v>1.421</v>
+      </c>
+      <c r="E52" s="7">
+        <v>256.448</v>
+      </c>
+      <c r="F52" s="7">
+        <v>274.459</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B53" s="6">
         <v>115.205</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C53" s="7">
         <v>4</v>
       </c>
       <c r="D53" s="7">
-        <v>0.644945</v>
-      </c>
-      <c r="E53" s="6">
+        <v>0.645</v>
+      </c>
+      <c r="E53" s="7">
         <v>74.3</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F53" s="7">
         <v>74.3</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B54" s="6">
         <v>8.419</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="7">
         <v>1</v>
       </c>
       <c r="D54" s="7">
         <v>1.79</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E54" s="7">
         <v>15.07</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54" s="7">
         <v>15.07</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B55" s="9">
         <v>2012.197</v>
@@ -3184,10 +3043,10 @@
       </c>
       <c r="D55" s="7"/>
       <c r="E55" s="9">
-        <v>2959.16</v>
+        <v>2959.163</v>
       </c>
       <c r="F55" s="9">
-        <v>3108.68</v>
+        <v>3108.677</v>
       </c>
     </row>
   </sheetData>
